--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487925_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487925_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8724</v>
+        <v>3.6643</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0283</v>
+        <v>2.8496</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8441</v>
+        <v>0.8147</v>
       </c>
       <c r="G2" t="n">
         <v>2.2333</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2415</v>
+        <v>0.0334</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4378</v>
+        <v>0.2591</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1963</v>
+        <v>-0.2257</v>
       </c>
       <c r="V2" t="n">
         <v>1.3975</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4109</v>
+        <v>2.9737</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4865</v>
+        <v>3.8732</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.0756</v>
+        <v>-0.8995</v>
       </c>
       <c r="G3" t="n">
         <v>3.001</v>
@@ -688,13 +688,13 @@
         <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3394</v>
+        <v>-0.7765</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8482</v>
+        <v>-0.4615</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4912</v>
+        <v>-0.3151</v>
       </c>
       <c r="V3" t="n">
         <v>-0.7076</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3882</v>
+        <v>1.7391</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8774</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2656</v>
+        <v>2.295</v>
       </c>
       <c r="G4" t="n">
         <v>3.2751</v>
@@ -766,13 +766,13 @@
         <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2011</v>
+        <v>-0.8502</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7705</v>
+        <v>-0.4491</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4305</v>
+        <v>-0.4012</v>
       </c>
       <c r="V4" t="n">
         <v>-0.4776</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. LAFUENTE VELAZQUEZ</t>
+          <t>V. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0481</v>
+        <v>0.9563</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8757</v>
+        <v>-0.9764</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9238</v>
+        <v>1.9327</v>
       </c>
       <c r="G5" t="n">
-        <v>0.224</v>
+        <v>1.7056</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8635</v>
+        <v>0.7675</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0875</v>
+        <v>0.9381</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.08599999999999999</v>
+        <v>1.0608</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.704</v>
+        <v>0.7351</v>
       </c>
       <c r="L5" t="n">
-        <v>0.618</v>
+        <v>0.3257</v>
       </c>
       <c r="M5" t="n">
-        <v>0.31</v>
+        <v>0.6448</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1595</v>
+        <v>0.0324</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4695</v>
+        <v>0.6123</v>
       </c>
       <c r="P5" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-1.2487</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.0812</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-1.1042</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.3109</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.7932</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.4776</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.4776</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-2.2893</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.2893</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.824</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.1675</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-1.1675</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. MORENO MARTIN</t>
+          <t>L. GARCIA MUÑOZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0197</v>
+        <v>0.6333</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6194</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6391</v>
+        <v>0.711</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7056</v>
+        <v>0.6843</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7675</v>
+        <v>0.5627</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9381</v>
+        <v>0.1217</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0608</v>
+        <v>0.8682</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7351</v>
+        <v>0.2894</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3257</v>
+        <v>0.5788</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6448</v>
+        <v>-0.1839</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0324</v>
+        <v>0.2733</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6123</v>
+        <v>-0.4572</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.2487</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0812</v>
+        <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.0407</v>
+        <v>-0.9054</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9539</v>
+        <v>-0.1571</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0868</v>
+        <v>-0.7482</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4776</v>
+        <v>0.23</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.4776</v>
+        <v>0.4599</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>J. LAFUENTE VELAZQUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2026</v>
+        <v>-0.1439</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6787</v>
+        <v>-1.3044</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4761</v>
+        <v>1.1605</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6843</v>
+        <v>0.224</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5627</v>
+        <v>-0.8635</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1217</v>
+        <v>1.0875</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8682</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2894</v>
+        <v>-0.704</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5788</v>
+        <v>0.618</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1839</v>
+        <v>0.31</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2733</v>
+        <v>-0.1595</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4572</v>
+        <v>0.4695</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.2487</v>
+        <v>-2.2893</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8731</v>
+        <v>2.2893</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7413</v>
+        <v>-0.3679</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7581</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9831</v>
+        <v>-0.2713</v>
       </c>
       <c r="V7" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4599</v>
+        <v>1.1675</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2057</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6943</v>
+        <v>-2.272</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4886</v>
+        <v>1.6354</v>
       </c>
       <c r="G8" t="n">
         <v>0.9921</v>
@@ -1078,13 +1078,13 @@
         <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1103</v>
+        <v>-0.3206</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7887</v>
+        <v>0.211</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6785</v>
+        <v>-0.5317</v>
       </c>
       <c r="V8" t="n">
         <v>1.3975</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.429</v>
+        <v>-0.7161</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5779</v>
+        <v>-0.5127</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1489</v>
+        <v>-0.2034</v>
       </c>
       <c r="G9" t="n">
         <v>-1.9305</v>
@@ -1156,13 +1156,13 @@
         <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2747</v>
+        <v>-0.0124</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2519</v>
+        <v>-0.1866</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5266</v>
+        <v>0.1743</v>
       </c>
       <c r="V9" t="n">
         <v>-0.23</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0633</v>
+        <v>-0.7315</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7572</v>
+        <v>-1.5429</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6939</v>
+        <v>0.8114</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5578</v>
@@ -1234,13 +1234,13 @@
         <v>0.8325</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3379</v>
+        <v>-0.0062</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5219</v>
+        <v>-0.3076</v>
       </c>
       <c r="U10" t="n">
-        <v>0.184</v>
+        <v>0.3014</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6185</v>
+        <v>-1.1922</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8774</v>
+        <v>-0.5979</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7411</v>
+        <v>-0.5943000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2377</v>
@@ -1312,13 +1312,13 @@
         <v>0.8325</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5265</v>
+        <v>-0.1001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4443</v>
+        <v>-0.1648</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0822</v>
+        <v>0.0646</v>
       </c>
       <c r="V11" t="n">
         <v>0.3538</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.220199999999999</v>
+        <v>6.5464</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4432</v>
+        <v>-1.1171</v>
       </c>
       <c r="F12" t="n">
-        <v>7.663399999999998</v>
+        <v>7.663500000000001</v>
       </c>
       <c r="G12" t="n">
         <v>7.389399999999998</v>
@@ -1366,7 +1366,7 @@
         <v>9.227699999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>8.003300000000001</v>
+        <v>8.003299999999999</v>
       </c>
       <c r="L12" t="n">
         <v>1.2245</v>
@@ -1381,7 +1381,7 @@
         <v>-3.8779</v>
       </c>
       <c r="P12" t="n">
-        <v>2.081300000000001</v>
+        <v>2.0813</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.5277</v>
@@ -1390,13 +1390,13 @@
         <v>15.6089</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.7364</v>
+        <v>-4.4101</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.9903</v>
+        <v>-1.6641</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.746</v>
+        <v>-2.7461</v>
       </c>
       <c r="V12" t="n">
         <v>1.486</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>R. UKAWUBA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7062</v>
+        <v>3.368</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2387</v>
+        <v>2.7833</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4676</v>
+        <v>0.5847</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3919</v>
+        <v>1.9758</v>
       </c>
       <c r="H13" t="n">
-        <v>0.307</v>
+        <v>1.081</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0849</v>
+        <v>0.8948</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2453</v>
+        <v>3.119</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1277</v>
+        <v>2.0487</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1176</v>
+        <v>1.0703</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8532999999999999</v>
+        <v>-1.1432</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8207</v>
+        <v>-0.9677</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0326</v>
+        <v>-0.1755</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6286</v>
+        <v>0.5597</v>
       </c>
       <c r="T13" t="n">
-        <v>1.034</v>
+        <v>0.4749</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5946</v>
+        <v>0.0849</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4776</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X13" t="n">
-        <v>0.4776</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. UKAWUBA</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2134</v>
+        <v>2.1214</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2119</v>
+        <v>0.2743</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0015</v>
+        <v>1.8471</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9758</v>
+        <v>0.3919</v>
       </c>
       <c r="H14" t="n">
-        <v>1.081</v>
+        <v>0.307</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8948</v>
+        <v>0.0849</v>
       </c>
       <c r="J14" t="n">
-        <v>3.119</v>
+        <v>1.2453</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0487</v>
+        <v>1.1277</v>
       </c>
       <c r="L14" t="n">
-        <v>1.0703</v>
+        <v>0.1176</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1432</v>
+        <v>-0.8532999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9677</v>
+        <v>-0.8207</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1755</v>
+        <v>-0.0326</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8325</v>
+        <v>0.2081</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8731</v>
+        <v>1.2487</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4051</v>
+        <v>1.0437</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9035</v>
+        <v>0.0696</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4984</v>
+        <v>0.9741</v>
       </c>
       <c r="V14" t="n">
+        <v>0.4776</v>
+      </c>
+      <c r="W14" t="n">
         <v>0</v>
       </c>
-      <c r="W14" t="n">
-        <v>0.23</v>
-      </c>
       <c r="X14" t="n">
-        <v>-0.23</v>
+        <v>0.4776</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1251</v>
+        <v>-0.717</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.2122</v>
+        <v>-2.9623</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3373</v>
+        <v>2.2453</v>
       </c>
       <c r="G15" t="n">
         <v>-3.1618</v>
@@ -1624,13 +1624,13 @@
         <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>2.288</v>
+        <v>1.4459</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3445</v>
+        <v>0.5944</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9435</v>
+        <v>0.8515</v>
       </c>
       <c r="V15" t="n">
         <v>1.4152</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8205</v>
+        <v>-1.0459</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.481</v>
+        <v>-1.3738</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3395</v>
+        <v>0.3279</v>
       </c>
       <c r="G16" t="n">
         <v>-2.0122</v>
@@ -1702,13 +1702,13 @@
         <v>2.4974</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1403</v>
+        <v>0.6343</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1734</v>
+        <v>0.2806</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3137</v>
+        <v>0.3537</v>
       </c>
       <c r="V16" t="n">
         <v>0.1238</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8618</v>
+        <v>-1.9259</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2413</v>
+        <v>-1.9199</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3796</v>
+        <v>-0.006</v>
       </c>
       <c r="G17" t="n">
         <v>-1.8578</v>
@@ -1780,13 +1780,13 @@
         <v>1.4568</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1854</v>
+        <v>1.1213</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4377</v>
+        <v>0.7592</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7477</v>
+        <v>0.3621</v>
       </c>
       <c r="V17" t="n">
         <v>-1.3975</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.9463</v>
+        <v>-2.0225</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2753</v>
+        <v>0.1533</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.671</v>
+        <v>-2.1758</v>
       </c>
       <c r="G18" t="n">
         <v>0.4497</v>
@@ -1858,13 +1858,13 @@
         <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9767</v>
+        <v>-0.0529</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4195</v>
+        <v>0.0091</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5571</v>
+        <v>-0.0619</v>
       </c>
       <c r="V18" t="n">
         <v>-2.2112</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>K. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2084</v>
+        <v>-2.2413</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.4901</v>
+        <v>-1.6639</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2817</v>
+        <v>-0.5774</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9457</v>
+        <v>-4.1207</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.9895</v>
+        <v>-5.5804</v>
       </c>
       <c r="I19" t="n">
-        <v>3.9351</v>
+        <v>1.4597</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2972</v>
+        <v>-2.8794</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6339</v>
+        <v>-4.3718</v>
       </c>
       <c r="L19" t="n">
-        <v>3.931</v>
+        <v>1.4924</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3515</v>
+        <v>-1.2412</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3556</v>
+        <v>-1.2086</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0041</v>
+        <v>-0.0326</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.538</v>
+        <v>0.6244</v>
       </c>
       <c r="Q19" t="n">
-        <v>-5.4111</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2623</v>
+        <v>0.7951</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6062</v>
+        <v>0.6287</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3439</v>
+        <v>0.1664</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3538</v>
+        <v>0.4599</v>
       </c>
       <c r="W19" t="n">
-        <v>0.23</v>
+        <v>1.6275</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5838</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. TORRES CUEVAS</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4278</v>
+        <v>-2.3282</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.414</v>
+        <v>-2.9543</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0139</v>
+        <v>0.6261</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.1207</v>
+        <v>0.9457</v>
       </c>
       <c r="H20" t="n">
-        <v>-5.5804</v>
+        <v>-2.9895</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4597</v>
+        <v>3.9351</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.8794</v>
+        <v>2.2972</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.3718</v>
+        <v>-1.6339</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4924</v>
+        <v>3.931</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2412</v>
+        <v>-1.3515</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2086</v>
+        <v>-1.3556</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0326</v>
+        <v>0.0041</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6244</v>
+        <v>-3.538</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-5.4111</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3915</v>
+        <v>0.618</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1214</v>
+        <v>-0.0704</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2701</v>
+        <v>0.6884</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4599</v>
+        <v>-0.3538</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6275</v>
+        <v>0.23</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1675</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.2201</v>
+        <v>-4.791399999999999</v>
       </c>
       <c r="E21" t="n">
         <v>-7.6633</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4433</v>
+        <v>2.8719</v>
       </c>
       <c r="G21" t="n">
         <v>-7.389399999999999</v>
@@ -2092,13 +2092,13 @@
         <v>13.5277</v>
       </c>
       <c r="S21" t="n">
-        <v>4.7363</v>
+        <v>6.165100000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>2.746</v>
+        <v>2.7461</v>
       </c>
       <c r="U21" t="n">
-        <v>1.9904</v>
+        <v>3.4192</v>
       </c>
       <c r="V21" t="n">
         <v>-1.486</v>
